--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K325"/>
+  <dimension ref="A1:K327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13115,6 +13115,84 @@
       <c r="K325" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="C326" t="n">
+        <v>377.68</v>
+      </c>
+      <c r="D326" t="n">
+        <v>385.36</v>
+      </c>
+      <c r="E326" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="F326" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="G326" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="H326" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="I326" t="n">
+        <v>388.67</v>
+      </c>
+      <c r="J326" t="n">
+        <v>393.71</v>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="C327" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="D327" t="n">
+        <v>385.23</v>
+      </c>
+      <c r="E327" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="F327" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="G327" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="H327" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="I327" t="n">
+        <v>390.92</v>
+      </c>
+      <c r="J327" t="n">
+        <v>394.61</v>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B447"/>
+  <dimension ref="A1:B449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17602,6 +17680,26 @@
       </c>
       <c r="B447" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -17770,28 +17868,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.134940226397271</v>
+        <v>0.1238401777221406</v>
       </c>
       <c r="J2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05116693467275724</v>
+        <v>0.0429002590051446</v>
       </c>
       <c r="M2" t="n">
-        <v>3.497374802087986</v>
+        <v>3.53002347164637</v>
       </c>
       <c r="N2" t="n">
-        <v>18.49420276301649</v>
+        <v>18.87923715900432</v>
       </c>
       <c r="O2" t="n">
-        <v>4.300488665607258</v>
+        <v>4.345024414086107</v>
       </c>
       <c r="P2" t="n">
-        <v>386.6119984543067</v>
+        <v>386.7262806431067</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17848,28 +17946,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02088486391051768</v>
+        <v>0.01174434052076265</v>
       </c>
       <c r="J3" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K3" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001426527445644865</v>
+        <v>0.0004485724101925825</v>
       </c>
       <c r="M3" t="n">
-        <v>3.294361322111069</v>
+        <v>3.313286072489684</v>
       </c>
       <c r="N3" t="n">
-        <v>16.72305150369604</v>
+        <v>16.95875161928664</v>
       </c>
       <c r="O3" t="n">
-        <v>4.089382777840201</v>
+        <v>4.118100486788374</v>
       </c>
       <c r="P3" t="n">
-        <v>384.3763403341638</v>
+        <v>384.4704486990529</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17926,28 +18024,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03611032020935641</v>
+        <v>-0.03972140526984575</v>
       </c>
       <c r="J4" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K4" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003836990467939616</v>
+        <v>0.004688655049238322</v>
       </c>
       <c r="M4" t="n">
-        <v>3.270293496493297</v>
+        <v>3.266513117596872</v>
       </c>
       <c r="N4" t="n">
-        <v>18.54192008007447</v>
+        <v>18.48093355959611</v>
       </c>
       <c r="O4" t="n">
-        <v>4.306032986412723</v>
+        <v>4.298945633477598</v>
       </c>
       <c r="P4" t="n">
-        <v>389.2084616879461</v>
+        <v>389.2456402394921</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18004,28 +18102,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006591659345007669</v>
+        <v>0.002467805791117767</v>
       </c>
       <c r="J5" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K5" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001495715817706467</v>
+        <v>2.116041714805839e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.016279731027526</v>
+        <v>3.0182851295773</v>
       </c>
       <c r="N5" t="n">
-        <v>15.9084473733589</v>
+        <v>15.88007566953291</v>
       </c>
       <c r="O5" t="n">
-        <v>3.988539503798214</v>
+        <v>3.984981263385426</v>
       </c>
       <c r="P5" t="n">
-        <v>386.9634281646925</v>
+        <v>387.0058872288591</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18082,28 +18180,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1510862122089384</v>
+        <v>-0.1538894440107036</v>
       </c>
       <c r="J6" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K6" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0887012311763905</v>
+        <v>0.09264210213600099</v>
       </c>
       <c r="M6" t="n">
-        <v>2.730071629409625</v>
+        <v>2.727324225377424</v>
       </c>
       <c r="N6" t="n">
-        <v>12.84497127474766</v>
+        <v>12.79828886647389</v>
       </c>
       <c r="O6" t="n">
-        <v>3.583988180051333</v>
+        <v>3.577469617826809</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4290513423504</v>
+        <v>387.4579136480742</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18160,28 +18258,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003376371228821599</v>
+        <v>0.003305961633220917</v>
       </c>
       <c r="J7" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K7" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L7" t="n">
-        <v>3.389276502663296e-05</v>
+        <v>3.293583494490271e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.072629689056435</v>
+        <v>3.055889562452033</v>
       </c>
       <c r="N7" t="n">
-        <v>18.42175475048909</v>
+        <v>18.30950743427546</v>
       </c>
       <c r="O7" t="n">
-        <v>4.29205716999309</v>
+        <v>4.278961022757214</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0119127749803</v>
+        <v>387.0126398231356</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18238,28 +18336,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2559394142280388</v>
+        <v>-0.2518909359269197</v>
       </c>
       <c r="J8" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1904200342281741</v>
+        <v>0.186934899472358</v>
       </c>
       <c r="M8" t="n">
-        <v>3.056415165278573</v>
+        <v>3.054660331463829</v>
       </c>
       <c r="N8" t="n">
-        <v>15.30083102993061</v>
+        <v>15.2741715332561</v>
       </c>
       <c r="O8" t="n">
-        <v>3.911627670156071</v>
+        <v>3.90821846027779</v>
       </c>
       <c r="P8" t="n">
-        <v>391.0681361789867</v>
+        <v>391.0265160059463</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18316,28 +18414,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3094522964724083</v>
+        <v>-0.3095879276179217</v>
       </c>
       <c r="J9" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3401195105287834</v>
+        <v>0.3431896179946108</v>
       </c>
       <c r="M9" t="n">
-        <v>2.491914413495061</v>
+        <v>2.483512686544808</v>
       </c>
       <c r="N9" t="n">
-        <v>10.20739038504949</v>
+        <v>10.15246623382056</v>
       </c>
       <c r="O9" t="n">
-        <v>3.194900684692638</v>
+        <v>3.186293494614167</v>
       </c>
       <c r="P9" t="n">
-        <v>398.0469462235714</v>
+        <v>398.0483335648445</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18394,28 +18492,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3876875799241578</v>
+        <v>-0.3877614720813667</v>
       </c>
       <c r="J10" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K10" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3525195063450699</v>
+        <v>0.3556860854089626</v>
       </c>
       <c r="M10" t="n">
-        <v>2.718164808119471</v>
+        <v>2.70430286879687</v>
       </c>
       <c r="N10" t="n">
-        <v>15.16704147503772</v>
+        <v>15.07500961149463</v>
       </c>
       <c r="O10" t="n">
-        <v>3.894488602504534</v>
+        <v>3.882654969411347</v>
       </c>
       <c r="P10" t="n">
-        <v>404.4142235556227</v>
+        <v>404.4149803507917</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18453,7 +18551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K325"/>
+  <dimension ref="A1:K327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36969,6 +37067,120 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-36.046662449100836,174.54633250020362</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-36.047007614823364,174.54712022736524</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-36.04722875939521,174.54795717568211</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-36.047448536820696,174.54879005078885</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-36.04764268119907,174.5496450687156</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-36.04774217048312,174.5505256902633</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-36.04785686962239,174.55139730223644</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-36.04792475602005,174.55225443447975</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-36.047824201665875,174.55311596191223</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-36.04666481069105,174.54633112030845</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-36.047011642470146,174.54711799537748</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-36.04722986190672,174.5479566869251</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-36.04745324110229,174.54878851212035</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-36.04764690621375,174.54964392111393</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-36.047748382211324,174.55052432713842</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-36.04784962653492,174.55139843332952</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-36.04790447571091,174.5522546125303</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-36.04781612127983,174.55311507631563</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K327"/>
+  <dimension ref="A1:K328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13193,6 +13193,45 @@
       <c r="K327" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="C328" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="D328" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="E328" t="n">
+        <v>383.71</v>
+      </c>
+      <c r="F328" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="G328" t="n">
+        <v>385.81</v>
+      </c>
+      <c r="H328" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="I328" t="n">
+        <v>390.66</v>
+      </c>
+      <c r="J328" t="n">
+        <v>393.92</v>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17700,6 +17739,16 @@
       </c>
       <c r="B449" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -17868,28 +17917,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1238401777221406</v>
+        <v>0.1182731226598556</v>
       </c>
       <c r="J2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0429002590051446</v>
+        <v>0.03903334705455663</v>
       </c>
       <c r="M2" t="n">
-        <v>3.53002347164637</v>
+        <v>3.546158801093283</v>
       </c>
       <c r="N2" t="n">
-        <v>18.87923715900432</v>
+        <v>19.07339151632704</v>
       </c>
       <c r="O2" t="n">
-        <v>4.345024414086107</v>
+        <v>4.367309413852772</v>
       </c>
       <c r="P2" t="n">
-        <v>386.7262806431067</v>
+        <v>386.7839008975249</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17946,28 +17995,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01174434052076265</v>
+        <v>0.007756863867707019</v>
       </c>
       <c r="J3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004485724101925825</v>
+        <v>0.0001955690138792932</v>
       </c>
       <c r="M3" t="n">
-        <v>3.313286072489684</v>
+        <v>3.319984773713391</v>
       </c>
       <c r="N3" t="n">
-        <v>16.95875161928664</v>
+        <v>17.03611736854299</v>
       </c>
       <c r="O3" t="n">
-        <v>4.118100486788374</v>
+        <v>4.127483176046026</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4704486990529</v>
+        <v>384.5117199666558</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18024,28 +18073,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03972140526984575</v>
+        <v>-0.0418024729275764</v>
       </c>
       <c r="J4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004688655049238322</v>
+        <v>0.005215471564280039</v>
       </c>
       <c r="M4" t="n">
-        <v>3.266513117596872</v>
+        <v>3.265830680952288</v>
       </c>
       <c r="N4" t="n">
-        <v>18.48093355959611</v>
+        <v>18.45961596673714</v>
       </c>
       <c r="O4" t="n">
-        <v>4.298945633477598</v>
+        <v>4.296465520254659</v>
       </c>
       <c r="P4" t="n">
-        <v>389.2456402394921</v>
+        <v>389.2671797512372</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18102,28 +18151,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002467805791117767</v>
+        <v>0.000415562560195993</v>
       </c>
       <c r="J5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>2.116041714805839e-05</v>
+        <v>6.028307671934741e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0182851295773</v>
+        <v>3.01931127601512</v>
       </c>
       <c r="N5" t="n">
-        <v>15.88007566953291</v>
+        <v>15.86574345483929</v>
       </c>
       <c r="O5" t="n">
-        <v>3.984981263385426</v>
+        <v>3.983182578647292</v>
       </c>
       <c r="P5" t="n">
-        <v>387.0058872288591</v>
+        <v>387.0271284013949</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18180,28 +18229,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1538894440107036</v>
+        <v>-0.1552978583233454</v>
       </c>
       <c r="J6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09264210213600099</v>
+        <v>0.09465787801221515</v>
       </c>
       <c r="M6" t="n">
-        <v>2.727324225377424</v>
+        <v>2.72604976218989</v>
       </c>
       <c r="N6" t="n">
-        <v>12.79828886647389</v>
+        <v>12.77527237431081</v>
       </c>
       <c r="O6" t="n">
-        <v>3.577469617826809</v>
+        <v>3.574251302624203</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4579136480742</v>
+        <v>387.4724910485333</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18258,28 +18307,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003305961633220917</v>
+        <v>0.00251993596547556</v>
       </c>
       <c r="J7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>3.293583494490271e-05</v>
+        <v>1.926140454266978e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.055889562452033</v>
+        <v>3.050063523655753</v>
       </c>
       <c r="N7" t="n">
-        <v>18.30950743427546</v>
+        <v>18.25853653605143</v>
       </c>
       <c r="O7" t="n">
-        <v>4.278961022757214</v>
+        <v>4.273000881821981</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0126398231356</v>
+        <v>387.0207753631021</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18336,28 +18385,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2518909359269197</v>
+        <v>-0.2500621324338805</v>
       </c>
       <c r="J8" t="n">
+        <v>327</v>
+      </c>
+      <c r="K8" t="n">
         <v>326</v>
       </c>
-      <c r="K8" t="n">
-        <v>325</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.186934899472358</v>
+        <v>0.1854846131736819</v>
       </c>
       <c r="M8" t="n">
-        <v>3.054660331463829</v>
+        <v>3.052877825872105</v>
       </c>
       <c r="N8" t="n">
-        <v>15.2741715332561</v>
+        <v>15.25458210101458</v>
       </c>
       <c r="O8" t="n">
-        <v>3.90821846027779</v>
+        <v>3.905711471808252</v>
       </c>
       <c r="P8" t="n">
-        <v>391.0265160059463</v>
+        <v>391.007615964388</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18414,28 +18463,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3095879276179217</v>
+        <v>-0.3091040555998699</v>
       </c>
       <c r="J9" t="n">
+        <v>327</v>
+      </c>
+      <c r="K9" t="n">
         <v>326</v>
       </c>
-      <c r="K9" t="n">
-        <v>325</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3431896179946108</v>
+        <v>0.3439733187006057</v>
       </c>
       <c r="M9" t="n">
-        <v>2.483512686544808</v>
+        <v>2.478310136528548</v>
       </c>
       <c r="N9" t="n">
-        <v>10.15246623382056</v>
+        <v>10.12323229614982</v>
       </c>
       <c r="O9" t="n">
-        <v>3.186293494614167</v>
+        <v>3.181702735352538</v>
       </c>
       <c r="P9" t="n">
-        <v>398.0483335648445</v>
+        <v>398.0433329175444</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18492,28 +18541,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3877614720813667</v>
+        <v>-0.3879134714535002</v>
       </c>
       <c r="J10" t="n">
+        <v>327</v>
+      </c>
+      <c r="K10" t="n">
         <v>326</v>
       </c>
-      <c r="K10" t="n">
-        <v>325</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.3556860854089626</v>
+        <v>0.3574212303134817</v>
       </c>
       <c r="M10" t="n">
-        <v>2.70430286879687</v>
+        <v>2.696880090731358</v>
       </c>
       <c r="N10" t="n">
-        <v>15.07500961149463</v>
+        <v>15.02895558820569</v>
       </c>
       <c r="O10" t="n">
-        <v>3.882654969411347</v>
+        <v>3.876719694304153</v>
       </c>
       <c r="P10" t="n">
-        <v>404.4149803507917</v>
+        <v>404.4165512108984</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18551,7 +18600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K327"/>
+  <dimension ref="A1:K328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37181,6 +37230,63 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-36.04666505499348,174.54633097756067</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-36.04700292960154,174.54712282375888</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-36.047233593484144,174.5479550326705</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-36.04745132454312,174.5487891389853</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-36.04764540985439,174.5496443275562</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-36.047756191241035,174.55052261349536</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-36.04785579657239,174.5513974698058</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-36.047906819213296,174.55225459195555</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-36.04782231624247,174.553115755273</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K328"/>
+  <dimension ref="A1:K329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13232,6 +13232,45 @@
       <c r="K328" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>379.47</v>
+      </c>
+      <c r="C329" t="n">
+        <v>377.96</v>
+      </c>
+      <c r="D329" t="n">
+        <v>384.31</v>
+      </c>
+      <c r="E329" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="F329" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="G329" t="n">
+        <v>384.98</v>
+      </c>
+      <c r="H329" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="I329" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="J329" t="n">
+        <v>395.1</v>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B450"/>
+  <dimension ref="A1:B451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17749,6 +17788,16 @@
       </c>
       <c r="B450" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -17917,28 +17966,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1182731226598556</v>
+        <v>0.1118654047871653</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03903334705455663</v>
+        <v>0.03471523590755898</v>
       </c>
       <c r="M2" t="n">
-        <v>3.546158801093283</v>
+        <v>3.566587599062379</v>
       </c>
       <c r="N2" t="n">
-        <v>19.07339151632704</v>
+        <v>19.34536197044388</v>
       </c>
       <c r="O2" t="n">
-        <v>4.367309413852772</v>
+        <v>4.398336273006406</v>
       </c>
       <c r="P2" t="n">
-        <v>386.7839008975249</v>
+        <v>386.850661361598</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17995,28 +18044,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007756863867707019</v>
+        <v>0.003617892257851206</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001955690138792932</v>
+        <v>4.250014298412541e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.319984773713391</v>
+        <v>3.327598818106106</v>
       </c>
       <c r="N3" t="n">
-        <v>17.03611736854299</v>
+        <v>17.12191521270523</v>
       </c>
       <c r="O3" t="n">
-        <v>4.127483176046026</v>
+        <v>4.137863604893862</v>
       </c>
       <c r="P3" t="n">
-        <v>384.5117199666558</v>
+        <v>384.5548429116651</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18073,28 +18122,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0418024729275764</v>
+        <v>-0.04416201312378398</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005215471564280039</v>
+        <v>0.005843202043831042</v>
       </c>
       <c r="M4" t="n">
-        <v>3.265830680952288</v>
+        <v>3.266248048942367</v>
       </c>
       <c r="N4" t="n">
-        <v>18.45961596673714</v>
+        <v>18.44809985731983</v>
       </c>
       <c r="O4" t="n">
-        <v>4.296465520254659</v>
+        <v>4.295125127085337</v>
       </c>
       <c r="P4" t="n">
-        <v>389.2671797512372</v>
+        <v>389.2917632303522</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18151,28 +18200,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000415562560195993</v>
+        <v>-0.002330104834125452</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>6.028307671934741e-07</v>
+        <v>1.901066094711634e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.01931127601512</v>
+        <v>3.023733687976097</v>
       </c>
       <c r="N5" t="n">
-        <v>15.86574345483929</v>
+        <v>15.87798479888417</v>
       </c>
       <c r="O5" t="n">
-        <v>3.983182578647292</v>
+        <v>3.984718910900011</v>
       </c>
       <c r="P5" t="n">
-        <v>387.0271284013949</v>
+        <v>387.0557348464783</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18229,28 +18278,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1552978583233454</v>
+        <v>-0.1564205274338151</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09465787801221515</v>
+        <v>0.0964295128331919</v>
       </c>
       <c r="M6" t="n">
-        <v>2.72604976218989</v>
+        <v>2.723275982297571</v>
       </c>
       <c r="N6" t="n">
-        <v>12.77527237431081</v>
+        <v>12.74645711848626</v>
       </c>
       <c r="O6" t="n">
-        <v>3.574251302624203</v>
+        <v>3.570218077160871</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4724910485333</v>
+        <v>387.4841878666992</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18307,28 +18356,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00251993596547556</v>
+        <v>0.001227590274389477</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>1.926140454266978e-05</v>
+        <v>4.599331104637727e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.050063523655753</v>
+        <v>3.046455219694409</v>
       </c>
       <c r="N7" t="n">
-        <v>18.25853653605143</v>
+        <v>18.21629865274528</v>
       </c>
       <c r="O7" t="n">
-        <v>4.273000881821981</v>
+        <v>4.268055605629486</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0207753631021</v>
+        <v>387.0342400005586</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18385,28 +18434,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2500621324338805</v>
+        <v>-0.2485142954284149</v>
       </c>
       <c r="J8" t="n">
+        <v>328</v>
+      </c>
+      <c r="K8" t="n">
         <v>327</v>
       </c>
-      <c r="K8" t="n">
-        <v>326</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1854846131736819</v>
+        <v>0.1844600325114495</v>
       </c>
       <c r="M8" t="n">
-        <v>3.052877825872105</v>
+        <v>3.049845153267738</v>
       </c>
       <c r="N8" t="n">
-        <v>15.25458210101458</v>
+        <v>15.22725243156757</v>
       </c>
       <c r="O8" t="n">
-        <v>3.905711471808252</v>
+        <v>3.902211223340886</v>
       </c>
       <c r="P8" t="n">
-        <v>391.007615964388</v>
+        <v>390.9915132113014</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18463,28 +18512,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3091040555998699</v>
+        <v>-0.3068786596622864</v>
       </c>
       <c r="J9" t="n">
+        <v>328</v>
+      </c>
+      <c r="K9" t="n">
         <v>327</v>
       </c>
-      <c r="K9" t="n">
-        <v>326</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3439733187006057</v>
+        <v>0.3413809219102248</v>
       </c>
       <c r="M9" t="n">
-        <v>2.478310136528548</v>
+        <v>2.48166276944083</v>
       </c>
       <c r="N9" t="n">
-        <v>10.12323229614982</v>
+        <v>10.1322119005565</v>
       </c>
       <c r="O9" t="n">
-        <v>3.181702735352538</v>
+        <v>3.183113554455212</v>
       </c>
       <c r="P9" t="n">
-        <v>398.0433329175444</v>
+        <v>398.0201812541738</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18541,28 +18590,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3879134714535002</v>
+        <v>-0.3873097385286518</v>
       </c>
       <c r="J10" t="n">
+        <v>328</v>
+      </c>
+      <c r="K10" t="n">
         <v>327</v>
       </c>
-      <c r="K10" t="n">
-        <v>326</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.3574212303134817</v>
+        <v>0.3582439113937984</v>
       </c>
       <c r="M10" t="n">
-        <v>2.696880090731358</v>
+        <v>2.691188276783621</v>
       </c>
       <c r="N10" t="n">
-        <v>15.02895558820569</v>
+        <v>14.98593486137159</v>
       </c>
       <c r="O10" t="n">
-        <v>3.876719694304153</v>
+        <v>3.871167118760386</v>
       </c>
       <c r="P10" t="n">
-        <v>404.4165512108984</v>
+        <v>404.410270341411</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18600,7 +18649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K328"/>
+  <dimension ref="A1:K329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37287,6 +37336,63 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-36.046676537207674,174.54632426841397</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-36.04700531331089,174.54712150278672</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-36.047237664295864,174.54795322802894</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-36.04746134292052,174.54878586219084</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-36.04764171296652,174.54964533170764</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-36.04776355657586,174.55052099721814</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-36.04786008877236,174.55139679952836</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-36.04788158149515,174.5522548135297</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-36.04781172195853,174.5531145941576</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K329"/>
+  <dimension ref="A1:K333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13271,6 +13271,162 @@
       <c r="K329" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="C330" t="n">
+        <v>379.63</v>
+      </c>
+      <c r="D330" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="E330" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="F330" t="n">
+        <v>383.14</v>
+      </c>
+      <c r="G330" t="n">
+        <v>386.91</v>
+      </c>
+      <c r="H330" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="I330" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="J330" t="n">
+        <v>396.83</v>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>383.54</v>
+      </c>
+      <c r="C331" t="n">
+        <v>378.76</v>
+      </c>
+      <c r="D331" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="E331" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="F331" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="G331" t="n">
+        <v>386.64</v>
+      </c>
+      <c r="H331" t="n">
+        <v>387.16</v>
+      </c>
+      <c r="I331" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="J331" t="n">
+        <v>396.21</v>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>383.03</v>
+      </c>
+      <c r="C332" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="D332" t="n">
+        <v>384.09</v>
+      </c>
+      <c r="E332" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="F332" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="G332" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="H332" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="I332" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="J332" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="C333" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="D333" t="n">
+        <v>383.35</v>
+      </c>
+      <c r="E333" t="n">
+        <v>384.25</v>
+      </c>
+      <c r="F333" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="G333" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="H333" t="n">
+        <v>384.97</v>
+      </c>
+      <c r="I333" t="n">
+        <v>392.12</v>
+      </c>
+      <c r="J333" t="n">
+        <v>394.14</v>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B451"/>
+  <dimension ref="A1:B455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17798,6 +17954,46 @@
       </c>
       <c r="B451" t="n">
         <v>1.01</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>
@@ -17966,28 +18162,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1118654047871653</v>
+        <v>0.09615541728623096</v>
       </c>
       <c r="J2" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03471523590755898</v>
+        <v>0.02591454583210084</v>
       </c>
       <c r="M2" t="n">
-        <v>3.566587599062379</v>
+        <v>3.599085011718054</v>
       </c>
       <c r="N2" t="n">
-        <v>19.34536197044388</v>
+        <v>19.61682446432048</v>
       </c>
       <c r="O2" t="n">
-        <v>4.398336273006406</v>
+        <v>4.429088446206565</v>
       </c>
       <c r="P2" t="n">
-        <v>386.850661361598</v>
+        <v>387.0151726855013</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18044,28 +18240,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003617892257851206</v>
+        <v>-0.01062377593446394</v>
       </c>
       <c r="J3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L3" t="n">
-        <v>4.250014298412541e-05</v>
+        <v>0.0003673855117662939</v>
       </c>
       <c r="M3" t="n">
-        <v>3.327598818106106</v>
+        <v>3.349896800724448</v>
       </c>
       <c r="N3" t="n">
-        <v>17.12191521270523</v>
+        <v>17.33420516588754</v>
       </c>
       <c r="O3" t="n">
-        <v>4.137863604893862</v>
+        <v>4.1634367013187</v>
       </c>
       <c r="P3" t="n">
-        <v>384.5548429116651</v>
+        <v>384.7039951856772</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18122,28 +18318,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04416201312378398</v>
+        <v>-0.05119228345782217</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005843202043831042</v>
+        <v>0.007994084272009538</v>
       </c>
       <c r="M4" t="n">
-        <v>3.266248048942367</v>
+        <v>3.257459627670496</v>
       </c>
       <c r="N4" t="n">
-        <v>18.44809985731983</v>
+        <v>18.35617881038588</v>
       </c>
       <c r="O4" t="n">
-        <v>4.295125127085337</v>
+        <v>4.284411139279922</v>
       </c>
       <c r="P4" t="n">
-        <v>389.2917632303522</v>
+        <v>389.3654239974516</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18200,28 +18396,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.002330104834125452</v>
+        <v>-0.008801639738843962</v>
       </c>
       <c r="J5" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L5" t="n">
-        <v>1.901066094711634e-05</v>
+        <v>0.0002771629561864053</v>
       </c>
       <c r="M5" t="n">
-        <v>3.023733687976097</v>
+        <v>3.020138085195553</v>
       </c>
       <c r="N5" t="n">
-        <v>15.87798479888417</v>
+        <v>15.7724565946633</v>
       </c>
       <c r="O5" t="n">
-        <v>3.984718910900011</v>
+        <v>3.971455223801888</v>
       </c>
       <c r="P5" t="n">
-        <v>387.0557348464783</v>
+        <v>387.1235055014179</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18278,28 +18474,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1564205274338151</v>
+        <v>-0.157485506974142</v>
       </c>
       <c r="J6" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0964295128331919</v>
+        <v>0.1000247480178907</v>
       </c>
       <c r="M6" t="n">
-        <v>2.723275982297571</v>
+        <v>2.695658001333728</v>
       </c>
       <c r="N6" t="n">
-        <v>12.74645711848626</v>
+        <v>12.59598175129637</v>
       </c>
       <c r="O6" t="n">
-        <v>3.570218077160871</v>
+        <v>3.549081818061733</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4841878666992</v>
+        <v>387.4953463072381</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18356,28 +18552,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001227590274389477</v>
+        <v>-0.001194458028731394</v>
       </c>
       <c r="J7" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>4.599331104637727e-06</v>
+        <v>4.470090813613048e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.046455219694409</v>
+        <v>3.020286427876224</v>
       </c>
       <c r="N7" t="n">
-        <v>18.21629865274528</v>
+        <v>18.01570393826691</v>
       </c>
       <c r="O7" t="n">
-        <v>4.268055605629486</v>
+        <v>4.244491010506079</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0342400005586</v>
+        <v>387.0596193712586</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18434,28 +18630,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2485142954284149</v>
+        <v>-0.2428024195553213</v>
       </c>
       <c r="J8" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1844600325114495</v>
+        <v>0.1806478868893274</v>
       </c>
       <c r="M8" t="n">
-        <v>3.049845153267738</v>
+        <v>3.035910492056678</v>
       </c>
       <c r="N8" t="n">
-        <v>15.22725243156757</v>
+        <v>15.13845279435612</v>
       </c>
       <c r="O8" t="n">
-        <v>3.902211223340886</v>
+        <v>3.890816468860503</v>
       </c>
       <c r="P8" t="n">
-        <v>390.9915132113014</v>
+        <v>390.9318262509933</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18512,28 +18708,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3068786596622864</v>
+        <v>-0.2978214194758042</v>
       </c>
       <c r="J9" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K9" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3413809219102248</v>
+        <v>0.3300496781765896</v>
       </c>
       <c r="M9" t="n">
-        <v>2.48166276944083</v>
+        <v>2.495496889390779</v>
       </c>
       <c r="N9" t="n">
-        <v>10.1322119005565</v>
+        <v>10.19325580369857</v>
       </c>
       <c r="O9" t="n">
-        <v>3.183113554455212</v>
+        <v>3.192687865059559</v>
       </c>
       <c r="P9" t="n">
-        <v>398.0201812541738</v>
+        <v>397.9255028401515</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18590,28 +18786,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3873097385286518</v>
+        <v>-0.3845877631812164</v>
       </c>
       <c r="J10" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K10" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3582439113937984</v>
+        <v>0.3607115414974238</v>
       </c>
       <c r="M10" t="n">
-        <v>2.691188276783621</v>
+        <v>2.672426514319779</v>
       </c>
       <c r="N10" t="n">
-        <v>14.98593486137159</v>
+        <v>14.84108071834913</v>
       </c>
       <c r="O10" t="n">
-        <v>3.871167118760386</v>
+        <v>3.85241232455057</v>
       </c>
       <c r="P10" t="n">
-        <v>404.410270341411</v>
+        <v>404.3818388010588</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18649,7 +18845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K329"/>
+  <dimension ref="A1:K333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37393,6 +37589,234 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-36.0466473837837,174.54634130298132</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-36.04699158643271,174.5471291097633</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-36.04721154325361,174.54796480780914</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-36.04744601044725,174.54879087711075</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-36.04762736552068,174.5496492287707</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-36.04774642995388,174.55052475554913</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-36.04784077387244,174.55139981577634</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-36.04786580792126,174.55225495201364</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-36.04779618966082,174.55311289184496</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-36.046643393510415,174.54634363452726</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-36.046998737560926,174.54712514684766</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-36.04722477339203,174.54795894272658</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-36.04744470370236,174.5487913045186</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-36.04762771760525,174.54964913313728</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-36.0477488259062,174.55052422977235</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-36.04785767440989,174.55139717655942</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-36.04787653395151,174.55225485784456</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-36.04780175614903,174.55311350192224</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-36.04664754665199,174.54634120781617</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-36.047002272026546,174.547123188165</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-36.04723953008455,174.5479524009015</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-36.04744827547171,174.54879013627044</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-36.047632030641125,174.54964796162764</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-36.047763112880986,174.55052109458424</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-36.04786929911813,174.55139536122448</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-36.04788392499755,174.55225479295495</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-36.04782429144794,174.55311597175222</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-36.0466450221934,174.5463426828759</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-36.04700523111402,174.54712154833746</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-36.04724580591922,174.54794961874526</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-36.04744662026154,174.54879067765376</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-36.04763211866227,174.54964793771927</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-36.04775778854256,174.55052226297744</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-36.04787725757222,174.55139411841796</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-36.04789365954599,174.55225470749065</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-36.04782034103699,174.55311553879383</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K333"/>
+  <dimension ref="A1:K336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13425,6 +13425,123 @@
         <v>394.14</v>
       </c>
       <c r="K333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>386.39</v>
+      </c>
+      <c r="C334" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="D334" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="E334" t="n">
+        <v>385.07</v>
+      </c>
+      <c r="F334" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="G334" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="H334" t="n">
+        <v>386</v>
+      </c>
+      <c r="I334" t="n">
+        <v>393.14</v>
+      </c>
+      <c r="J334" t="n">
+        <v>394.75</v>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="C335" t="n">
+        <v>381.38</v>
+      </c>
+      <c r="D335" t="n">
+        <v>385.32</v>
+      </c>
+      <c r="E335" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="F335" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="G335" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="H335" t="n">
+        <v>385</v>
+      </c>
+      <c r="I335" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="J335" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="C336" t="n">
+        <v>381.38</v>
+      </c>
+      <c r="D336" t="n">
+        <v>385.32</v>
+      </c>
+      <c r="E336" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="F336" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="G336" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="H336" t="n">
+        <v>384.92</v>
+      </c>
+      <c r="I336" t="n">
+        <v>390.83</v>
+      </c>
+      <c r="J336" t="n">
+        <v>393.21</v>
+      </c>
+      <c r="K336" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13441,7 +13558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B455"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17994,6 +18111,36 @@
       </c>
       <c r="B455" t="n">
         <v>-0.15</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -18162,28 +18309,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09615541728623096</v>
+        <v>0.09185010189584689</v>
       </c>
       <c r="J2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02591454583210084</v>
+        <v>0.02410003232762226</v>
       </c>
       <c r="M2" t="n">
-        <v>3.599085011718054</v>
+        <v>3.587614692345062</v>
       </c>
       <c r="N2" t="n">
-        <v>19.61682446432048</v>
+        <v>19.49605639315442</v>
       </c>
       <c r="O2" t="n">
-        <v>4.429088446206565</v>
+        <v>4.415433885039433</v>
       </c>
       <c r="P2" t="n">
-        <v>387.0151726855013</v>
+        <v>387.0604848102794</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18240,28 +18387,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01062377593446394</v>
+        <v>-0.01654873938422049</v>
       </c>
       <c r="J3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003673855117662939</v>
+        <v>0.0009036190219676721</v>
       </c>
       <c r="M3" t="n">
-        <v>3.349896800724448</v>
+        <v>3.346646298887238</v>
       </c>
       <c r="N3" t="n">
-        <v>17.33420516588754</v>
+        <v>17.28031533886094</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1634367013187</v>
+        <v>4.156959867362318</v>
       </c>
       <c r="P3" t="n">
-        <v>384.7039951856772</v>
+        <v>384.7663567524747</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18318,28 +18465,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05119228345782217</v>
+        <v>-0.05596357269430086</v>
       </c>
       <c r="J4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007994084272009538</v>
+        <v>0.009695472368147828</v>
       </c>
       <c r="M4" t="n">
-        <v>3.257459627670496</v>
+        <v>3.24892943396967</v>
       </c>
       <c r="N4" t="n">
-        <v>18.35617881038588</v>
+        <v>18.25620334794121</v>
       </c>
       <c r="O4" t="n">
-        <v>4.284411139279922</v>
+        <v>4.272727857931184</v>
       </c>
       <c r="P4" t="n">
-        <v>389.3654239974516</v>
+        <v>389.4156470087644</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18396,28 +18543,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008801639738843962</v>
+        <v>-0.01108696783067474</v>
       </c>
       <c r="J5" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K5" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002771629561864053</v>
+        <v>0.0004481208312629992</v>
       </c>
       <c r="M5" t="n">
-        <v>3.020138085195553</v>
+        <v>3.004552381877947</v>
       </c>
       <c r="N5" t="n">
-        <v>15.7724565946633</v>
+        <v>15.64716243019394</v>
       </c>
       <c r="O5" t="n">
-        <v>3.971455223801888</v>
+        <v>3.95564943216584</v>
       </c>
       <c r="P5" t="n">
-        <v>387.1235055014179</v>
+        <v>387.1475567956645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18474,28 +18621,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.157485506974142</v>
+        <v>-0.1541594150720383</v>
       </c>
       <c r="J6" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K6" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1000247480178907</v>
+        <v>0.09776689957291729</v>
       </c>
       <c r="M6" t="n">
-        <v>2.695658001333728</v>
+        <v>2.688731600084711</v>
       </c>
       <c r="N6" t="n">
-        <v>12.59598175129637</v>
+        <v>12.51603675669591</v>
       </c>
       <c r="O6" t="n">
-        <v>3.549081818061733</v>
+        <v>3.537801118872556</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4953463072381</v>
+        <v>387.4603307321024</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18552,28 +18699,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.001194458028731394</v>
+        <v>-0.00218377586743275</v>
       </c>
       <c r="J7" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K7" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L7" t="n">
-        <v>4.470090813613048e-06</v>
+        <v>1.523983267903706e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.020286427876224</v>
+        <v>2.997471262520221</v>
       </c>
       <c r="N7" t="n">
-        <v>18.01570393826691</v>
+        <v>17.8578477620004</v>
       </c>
       <c r="O7" t="n">
-        <v>4.244491010506079</v>
+        <v>4.225854678287033</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0596193712586</v>
+        <v>387.0700341693791</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18630,28 +18777,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2428024195553213</v>
+        <v>-0.2412503855907938</v>
       </c>
       <c r="J8" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K8" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1806478868893274</v>
+        <v>0.1816206983478411</v>
       </c>
       <c r="M8" t="n">
-        <v>3.035910492056678</v>
+        <v>3.014821313153751</v>
       </c>
       <c r="N8" t="n">
-        <v>15.13845279435612</v>
+        <v>15.01146194198648</v>
       </c>
       <c r="O8" t="n">
-        <v>3.890816468860503</v>
+        <v>3.874462793986603</v>
       </c>
       <c r="P8" t="n">
-        <v>390.9318262509933</v>
+        <v>390.9155190309256</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18708,28 +18855,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2978214194758042</v>
+        <v>-0.2948233055147932</v>
       </c>
       <c r="J9" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K9" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3300496781765896</v>
+        <v>0.3292190300102824</v>
       </c>
       <c r="M9" t="n">
-        <v>2.495496889390779</v>
+        <v>2.487771421373857</v>
       </c>
       <c r="N9" t="n">
-        <v>10.19325580369857</v>
+        <v>10.13717832275514</v>
       </c>
       <c r="O9" t="n">
-        <v>3.192687865059559</v>
+        <v>3.183893579056174</v>
       </c>
       <c r="P9" t="n">
-        <v>397.9255028401515</v>
+        <v>397.8940030962414</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18786,28 +18933,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3845877631812164</v>
+        <v>-0.3848633481567118</v>
       </c>
       <c r="J10" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K10" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3607115414974238</v>
+        <v>0.365604882544857</v>
       </c>
       <c r="M10" t="n">
-        <v>2.672426514319779</v>
+        <v>2.654074573501898</v>
       </c>
       <c r="N10" t="n">
-        <v>14.84108071834913</v>
+        <v>14.71155616270498</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85241232455057</v>
+        <v>3.835564647181036</v>
       </c>
       <c r="P10" t="n">
-        <v>404.3818388010588</v>
+        <v>404.3847449985378</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18845,7 +18992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K333"/>
+  <dimension ref="A1:K336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37817,6 +37964,177 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-36.04662018477718,174.54635719555543</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-36.04698550386378,174.54713248051854</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-36.047230285949624,174.54795649894163</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-36.04743947672278,174.54879301414994</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-36.04761451443413,174.5496527193905</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-36.04775148807541,174.55052364557588</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-36.04786804722649,174.5513955567221</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-36.047884465805794,174.55225478820694</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-36.04781486433088,174.5531149385562</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-36.04661106415181,174.54636252479946</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-36.046977201979026,174.54713708114315</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-36.04722909862952,174.54795702529532</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-36.04743276876562,174.5487952081765</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-36.04760571231999,174.54965511022536</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-36.04774687364877,174.55052465818304</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-36.047876989309714,174.5513941603103</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-36.04790393490266,174.5522546172783</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-36.04782357319141,174.5531158930325</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-36.04661106415181,174.54636252479946</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-36.046977201979026,174.54713708114315</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-36.04722909862952,174.54795702529532</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-36.04743276876562,174.5487952081765</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-36.04760835295424,174.54965439297496</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-36.04775273042106,174.55052337295083</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-36.04787770467638,174.55139404859736</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-36.04790528692326,174.55225460540828</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-36.047828690769215,174.55311645391043</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
